--- a/BOM/solar-glow-drh-v4_0-BOM-assembly.xlsx
+++ b/BOM/solar-glow-drh-v4_0-BOM-assembly.xlsx
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AEM BUFSRC/CSRC buffer (re-picked audit #2; land sync 0603→0805 pending in KiCad)</t>
+          <t>AEM BUFSRC/CSRC buffer (re-picked audit #2; land sync 0603→0805 DONE, board-verified 2026-08-01)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1757,6 +1757,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
